--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eliotryan/Desktop/团支部/入党流程查询系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1940CA3-7F28-1C4E-B324-4BA7CBB9979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD550C68-B9EF-CA4D-BA0E-08411DF84A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="入党流程数据" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
   <si>
     <t>姓名</t>
   </si>
@@ -158,6 +158,10 @@
   </si>
   <si>
     <t>校党校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -682,6 +686,9 @@
         <v>45942</v>
       </c>
       <c r="G2" s="2"/>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="16">
       <c r="A3" s="5" t="s">
@@ -890,6 +897,9 @@
       <c r="F14" s="8">
         <v>45942</v>
       </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="16">
       <c r="A15" s="5" t="s">
@@ -923,7 +933,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="16">
+    <row r="17" spans="1:10" ht="16">
       <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
@@ -943,7 +953,7 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16">
+    <row r="18" spans="1:10" ht="16">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="F18" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="16">
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
@@ -982,8 +995,11 @@
       <c r="F19" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="16">
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -995,7 +1011,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="16">
+    <row r="21" spans="1:10" ht="16">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -1015,7 +1031,7 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16">
+    <row r="22" spans="1:10" ht="16">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -1035,7 +1051,7 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16">
+    <row r="23" spans="1:10" ht="16">
       <c r="A23" s="5" t="s">
         <v>28</v>
       </c>
@@ -1055,7 +1071,7 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16">
+    <row r="24" spans="1:10" ht="16">
       <c r="A24" s="5" t="s">
         <v>29</v>
       </c>
@@ -1067,7 +1083,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="16">
+    <row r="25" spans="1:10" ht="16">
       <c r="A25" s="5" t="s">
         <v>30</v>
       </c>
@@ -1086,8 +1102,11 @@
       <c r="F25" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="16">
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16">
       <c r="A26" s="5" t="s">
         <v>31</v>
       </c>
@@ -1106,8 +1125,11 @@
       <c r="F26" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="16">
+      <c r="J26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16">
       <c r="A27" s="5" t="s">
         <v>32</v>
       </c>
@@ -1119,7 +1141,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="16">
+    <row r="28" spans="1:10" ht="16">
       <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
@@ -1138,8 +1160,11 @@
       <c r="F28" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="16">
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16">
       <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
@@ -1159,7 +1184,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16">
+    <row r="30" spans="1:10" ht="16">
       <c r="A30" s="5" t="s">
         <v>35</v>
       </c>
@@ -1178,8 +1203,11 @@
       <c r="F30" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="16">
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16">
       <c r="A31" s="5" t="s">
         <v>36</v>
       </c>
@@ -1198,8 +1226,11 @@
       <c r="F31" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="16">
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16">
       <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
@@ -1211,7 +1242,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" ht="16">
+    <row r="33" spans="1:10" ht="16">
       <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
@@ -1230,8 +1261,11 @@
       <c r="F33" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="16">
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="16">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
@@ -1250,8 +1284,11 @@
       <c r="F34" s="8">
         <v>45942</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="16">
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="16">
       <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
@@ -1269,6 +1306,9 @@
       </c>
       <c r="F35" s="8">
         <v>45942</v>
+      </c>
+      <c r="J35" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eliotryan/Desktop/团支部/入党流程查询系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD550C68-B9EF-CA4D-BA0E-08411DF84A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF324F9-999B-DA4D-BDD1-3D2C779078CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="入党流程数据" sheetId="1" r:id="rId1"/>
@@ -153,15 +153,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>院党校</t>
+    <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>校党校</t>
+    <t>院党校培训</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
+    <t>校党校培训</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +628,8 @@
     <col min="6" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -660,10 +661,10 @@
         <v>42</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16">
@@ -687,7 +688,7 @@
       </c>
       <c r="G2" s="2"/>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16">
@@ -898,7 +899,7 @@
         <v>45942</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="16">
@@ -973,7 +974,7 @@
         <v>45942</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16">
@@ -996,7 +997,7 @@
         <v>45942</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16">
@@ -1103,7 +1104,7 @@
         <v>45942</v>
       </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16">
@@ -1126,7 +1127,7 @@
         <v>45942</v>
       </c>
       <c r="J26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16">
@@ -1161,7 +1162,7 @@
         <v>45942</v>
       </c>
       <c r="J28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16">
@@ -1204,7 +1205,7 @@
         <v>45942</v>
       </c>
       <c r="J30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16">
@@ -1227,7 +1228,7 @@
         <v>45942</v>
       </c>
       <c r="J31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16">
@@ -1262,7 +1263,7 @@
         <v>45942</v>
       </c>
       <c r="J33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16">
@@ -1285,7 +1286,7 @@
         <v>45942</v>
       </c>
       <c r="J34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16">
@@ -1308,7 +1309,7 @@
         <v>45942</v>
       </c>
       <c r="J35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -496,16 +496,16 @@
         <v>2025-11-20</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-03-10</v>
+        <v>2025-12-11</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>2026-03-01</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-04-10</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>2026-05-07</v>
       </c>
       <c r="K3" t="str">
         <v>是</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -458,13 +458,13 @@
         <v>2025-11-20</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-03-10</v>
+        <v>2025-11-28</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>2026-01-15</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-05-14</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -473,7 +473,7 @@
         <v>是</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>是</v>
       </c>
     </row>
     <row r="3">
@@ -546,10 +546,10 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>是</v>
       </c>
     </row>
     <row r="5">
@@ -566,16 +566,16 @@
         <v>2025-10-20</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2025-12-04</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2026-01-14</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>2026-04-16</v>
       </c>
       <c r="I5" t="str">
         <v/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1282,10 +1282,10 @@
         <v>2025200822</v>
       </c>
       <c r="C24" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>2026-06-11</v>
       </c>
       <c r="E24" t="str">
         <v/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -598,7 +598,7 @@
         <v>2025200837</v>
       </c>
       <c r="C6" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D6" t="str">
         <v>2025年9月14日</v>
@@ -636,7 +636,7 @@
         <v>2025200847</v>
       </c>
       <c r="C7" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D7" t="str">
         <v>2025年9月14日</v>
@@ -674,7 +674,7 @@
         <v>2025200844</v>
       </c>
       <c r="C8" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v>2025200850</v>
       </c>
       <c r="C9" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D9" t="str">
         <v>2025年9月12日</v>
@@ -750,7 +750,7 @@
         <v>2025200829</v>
       </c>
       <c r="C10" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -788,7 +788,7 @@
         <v>2025200825</v>
       </c>
       <c r="C11" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D11" t="str">
         <v>2025年9月14日</v>
@@ -826,7 +826,7 @@
         <v>2025200854</v>
       </c>
       <c r="C12" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D12" t="str">
         <v>2026年3月5日</v>
@@ -864,7 +864,7 @@
         <v>2025200838</v>
       </c>
       <c r="C13" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -902,7 +902,7 @@
         <v>2025200845</v>
       </c>
       <c r="C14" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D14" t="str">
         <v>2025年9月15日</v>
@@ -940,7 +940,7 @@
         <v>2025200831</v>
       </c>
       <c r="C15" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>2025200826</v>
       </c>
       <c r="C16" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D16" t="str">
         <v>2025年9月12日</v>
@@ -1016,7 +1016,7 @@
         <v>2025200848</v>
       </c>
       <c r="C17" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D17" t="str">
         <v>2026年4月18日</v>
@@ -1054,7 +1054,7 @@
         <v>2025200832</v>
       </c>
       <c r="C18" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D18" t="str">
         <v>2025年9月12日</v>
@@ -1092,7 +1092,7 @@
         <v>2025200855</v>
       </c>
       <c r="C19" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D19" t="str">
         <v>2025年9月18日</v>
@@ -1130,7 +1130,7 @@
         <v>2025200834</v>
       </c>
       <c r="C20" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -1168,7 +1168,7 @@
         <v>2025200851</v>
       </c>
       <c r="C21" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D21" t="str">
         <v>2025年9月13日</v>
@@ -1206,7 +1206,7 @@
         <v>2025200839</v>
       </c>
       <c r="C22" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D22" t="str">
         <v>2025年9月14日</v>
@@ -1244,7 +1244,7 @@
         <v>2025200830</v>
       </c>
       <c r="C23" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D23" t="str">
         <v>2025年9月15日</v>
@@ -1320,7 +1320,7 @@
         <v>2025200840</v>
       </c>
       <c r="C25" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D25" t="str">
         <v>2025年9月10日</v>
@@ -1358,7 +1358,7 @@
         <v>2025200846</v>
       </c>
       <c r="C26" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D26" t="str">
         <v>2025年9月12日</v>
@@ -1396,7 +1396,7 @@
         <v>2025200842</v>
       </c>
       <c r="C27" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D27" t="str">
         <v>2025年9月14日</v>
@@ -1434,7 +1434,7 @@
         <v>2025200835</v>
       </c>
       <c r="C28" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1472,7 +1472,7 @@
         <v>2025200833</v>
       </c>
       <c r="C29" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D29" t="str">
         <v>2025年9月13日</v>
@@ -1510,7 +1510,7 @@
         <v>2025200824</v>
       </c>
       <c r="C30" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D30" t="str">
         <v>2025年9月12日</v>
@@ -1548,7 +1548,7 @@
         <v>2025200828</v>
       </c>
       <c r="C31" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
         <v>2025200836</v>
       </c>
       <c r="C32" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D32" t="str">
         <v>2025年9月13日</v>
@@ -1624,7 +1624,7 @@
         <v>2025200849</v>
       </c>
       <c r="C33" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D33" t="str">
         <v>2025年9月18日</v>
@@ -1662,7 +1662,7 @@
         <v>2025200853</v>
       </c>
       <c r="C34" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D34" t="str">
         <v>2025年9月15日</v>
@@ -1700,7 +1700,7 @@
         <v>2025200852</v>
       </c>
       <c r="C35" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D35" t="str">
         <v>2025年9月15日</v>
@@ -1738,7 +1738,7 @@
         <v>2025200823</v>
       </c>
       <c r="C36" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>2025200827</v>
       </c>
       <c r="C37" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D37" t="str">
         <v>2025年9月10日</v>
@@ -1814,7 +1814,7 @@
         <v>2025200841</v>
       </c>
       <c r="C38" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D38" t="str">
         <v>2025年9月12日</v>
@@ -1852,7 +1852,7 @@
         <v>2025200843</v>
       </c>
       <c r="C39" t="str">
-        <v>2025级本科1班</v>
+        <v>2025级1班</v>
       </c>
       <c r="D39" t="str">
         <v>2025年9月12日</v>
